--- a/SampleFiles/SampleTemplate.xlsx
+++ b/SampleFiles/SampleTemplate.xlsx
@@ -88,6 +88,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -109,6 +110,7 @@
       <color rgb="FF000000"/>
       <name val="Cascadia Mono"/>
       <family val="0"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -153,12 +155,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -288,244 +294,244 @@
   <dimension ref="A1:E13"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.81"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18.26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13.81"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14.93"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="19.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13.81"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18.26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="13.81"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="19.38"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="0" t="s">
+      <c r="A2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="0" t="n">
+      <c r="C2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="E2" s="0" t="str">
-        <f aca="false">C2&amp;" colunn "&amp;D2</f>
-        <v>Sheet1 colunn 1</v>
+      <c r="E2" s="1" t="str">
+        <f aca="false">C2&amp;" column "&amp;D2</f>
+        <v>Sheet1 column 1</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="0" t="s">
+      <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="0" t="n">
+      <c r="C3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="E3" s="0" t="str">
-        <f aca="false">C3&amp;" colunn "&amp;D3</f>
-        <v>Sheet1 colunn 2</v>
+      <c r="E3" s="1" t="str">
+        <f aca="false">C3&amp;" column "&amp;D3</f>
+        <v>Sheet1 column 2</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="0" t="s">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="0" t="n">
+      <c r="C4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="E4" s="0" t="str">
-        <f aca="false">C4&amp;" colunn "&amp;D4</f>
-        <v>Sheet1 colunn 3</v>
+      <c r="E4" s="1" t="str">
+        <f aca="false">C4&amp;" column "&amp;D4</f>
+        <v>Sheet1 column 3</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="0" t="s">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" s="0" t="n">
+      <c r="C5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="E5" s="0" t="str">
-        <f aca="false">C5&amp;" colunn "&amp;D5</f>
-        <v>Sheet1 colunn 4</v>
+      <c r="E5" s="1" t="str">
+        <f aca="false">C5&amp;" column "&amp;D5</f>
+        <v>Sheet1 column 4</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="0" t="s">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="D6" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="E6" s="0" t="str">
-        <f aca="false">C6&amp;" colunn "&amp;D6</f>
-        <v>Sheet1 colunn 5</v>
+      <c r="C6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" s="1" t="str">
+        <f aca="false">C6&amp;" column "&amp;D6</f>
+        <v>Sheet1 column 5</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="0" t="s">
+      <c r="A7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="D7" s="0" t="n">
+      <c r="C7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="E7" s="0" t="str">
-        <f aca="false">C7&amp;" colunn "&amp;D7</f>
-        <v>Sheet1 colunn 6</v>
+      <c r="E7" s="1" t="str">
+        <f aca="false">C7&amp;" column "&amp;D7</f>
+        <v>Sheet1 column 6</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8" s="0" t="s">
+      <c r="A8" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="0" t="n">
+      <c r="D8" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="E8" s="0" t="str">
-        <f aca="false">C8&amp;" colunn "&amp;D8</f>
-        <v>Sheet2 colunn 1</v>
+      <c r="E8" s="1" t="str">
+        <f aca="false">C8&amp;" column "&amp;D8</f>
+        <v>Sheet2 column 1</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B9" s="0" t="s">
+      <c r="A9" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="0" t="n">
+      <c r="D9" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="E9" s="0" t="str">
-        <f aca="false">C9&amp;" colunn "&amp;D9</f>
-        <v>Sheet2 colunn 2</v>
+      <c r="E9" s="1" t="str">
+        <f aca="false">C9&amp;" column "&amp;D9</f>
+        <v>Sheet2 column 2</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B10" s="0" t="s">
+      <c r="A10" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="0" t="s">
+      <c r="C10" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="0" t="n">
+      <c r="D10" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="E10" s="0" t="str">
-        <f aca="false">C10&amp;" colunn "&amp;D10</f>
-        <v>Sheet2 colunn 3</v>
+      <c r="E10" s="1" t="str">
+        <f aca="false">C10&amp;" column "&amp;D10</f>
+        <v>Sheet2 column 3</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B11" s="0" t="s">
+      <c r="A11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="0" t="s">
+      <c r="C11" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="0" t="n">
+      <c r="D11" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="E11" s="0" t="str">
-        <f aca="false">C11&amp;" colunn "&amp;D11</f>
-        <v>Sheet2 colunn 4</v>
+      <c r="E11" s="1" t="str">
+        <f aca="false">C11&amp;" column "&amp;D11</f>
+        <v>Sheet2 column 4</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B12" s="0" t="s">
+      <c r="A12" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="0" t="s">
+      <c r="C12" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D12" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="E12" s="0" t="str">
-        <f aca="false">C12&amp;" colunn "&amp;D12</f>
-        <v>Sheet2 colunn 5</v>
+      <c r="D12" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="E12" s="1" t="str">
+        <f aca="false">C12&amp;" column "&amp;D12</f>
+        <v>Sheet2 column 5</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B13" s="0" t="s">
+      <c r="A13" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="0" t="s">
+      <c r="C13" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D13" s="0" t="n">
+      <c r="D13" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="E13" s="0" t="str">
-        <f aca="false">C13&amp;" colunn "&amp;D13</f>
-        <v>Sheet2 colunn 6</v>
+      <c r="E13" s="1" t="str">
+        <f aca="false">C13&amp;" column "&amp;D13</f>
+        <v>Sheet2 column 6</v>
       </c>
     </row>
   </sheetData>

--- a/SampleFiles/SampleTemplate.xlsx
+++ b/SampleFiles/SampleTemplate.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="29">
   <si>
     <t xml:space="preserve">SourceSheet</t>
   </si>
@@ -37,43 +37,76 @@
     <t xml:space="preserve">OutputColumnName</t>
   </si>
   <si>
-    <t xml:space="preserve">Sheet1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sheet2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G8</t>
+    <t xml:space="preserve">Budget</t>
   </si>
   <si>
     <t xml:space="preserve">B2</t>
   </si>
   <si>
-    <t xml:space="preserve">B1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L10</t>
+    <t xml:space="preserve">Budget Summary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Department Number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Department Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salaries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Travel Costs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supplies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fuel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Office Supplies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staffing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Benefits Costs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staffing Summary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yearly Hours</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annual Cost</t>
   </si>
 </sst>
 </file>
@@ -291,12 +324,12 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13.81"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18.26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="13.81"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15.62"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14.93"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="19.38"/>
   </cols>
@@ -326,14 +359,13 @@
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" s="1" t="str">
-        <f aca="false">C2&amp;" column "&amp;D2</f>
-        <v>Sheet1 column 1</v>
+        <v>7</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -341,17 +373,16 @@
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E3" s="1" t="str">
-        <f aca="false">C3&amp;" column "&amp;D3</f>
-        <v>Sheet1 column 2</v>
+        <v>8</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -359,17 +390,16 @@
         <v>5</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="E4" s="1" t="str">
-        <f aca="false">C4&amp;" column "&amp;D4</f>
-        <v>Sheet1 column 3</v>
+        <v>1</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -377,17 +407,16 @@
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="E5" s="1" t="str">
-        <f aca="false">C5&amp;" column "&amp;D5</f>
-        <v>Sheet1 column 4</v>
+        <v>2</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -395,17 +424,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="E6" s="1" t="str">
-        <f aca="false">C6&amp;" column "&amp;D6</f>
-        <v>Sheet1 column 5</v>
+        <v>3</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -413,17 +441,16 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="E7" s="1" t="str">
-        <f aca="false">C7&amp;" column "&amp;D7</f>
-        <v>Sheet1 column 6</v>
+        <v>4</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -431,109 +458,89 @@
         <v>5</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" s="1" t="str">
-        <f aca="false">C8&amp;" column "&amp;D8</f>
-        <v>Sheet2 column 1</v>
+        <v>5</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E9" s="1" t="str">
-        <f aca="false">C9&amp;" column "&amp;D9</f>
-        <v>Sheet2 column 2</v>
+        <v>6</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="E10" s="1" t="str">
-        <f aca="false">C10&amp;" column "&amp;D10</f>
-        <v>Sheet2 column 3</v>
+        <v>1</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="E11" s="1" t="str">
-        <f aca="false">C11&amp;" column "&amp;D11</f>
-        <v>Sheet2 column 4</v>
+        <v>2</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="E12" s="1" t="str">
-        <f aca="false">C12&amp;" column "&amp;D12</f>
-        <v>Sheet2 column 5</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="E13" s="1" t="str">
-        <f aca="false">C13&amp;" column "&amp;D13</f>
-        <v>Sheet2 column 6</v>
-      </c>
-    </row>
+        <v>3</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
